--- a/frontend/public/templates/sample_homework_template.xlsx
+++ b/frontend/public/templates/sample_homework_template.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,13 +28,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F2937"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,8 +58,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,21 +428,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>username</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>full_name</t>
         </is>
@@ -439,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>student1</t>
+          <t>student_user</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -449,14 +466,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Budi Santoso</t>
+          <t>Student User</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>student2</t>
+          <t>demo_student_1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -466,24 +483,58 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Siti Rahma</t>
+          <t>Demo Student One</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>instructor1</t>
+          <t>demo_student_2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>student</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Demo Student Two</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>demo_student_3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>student</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Demo Student Three</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>instructor_user</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>instructor</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Dr. Pak Dosen</t>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Instructor User</t>
         </is>
       </c>
     </row>
@@ -500,49 +551,60 @@
   </sheetPr>
   <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>course_ref</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>week</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>topic_kc_focus</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>target_task</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>deadline</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>starts_at</t>
         </is>
@@ -564,7 +626,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Homework 1: Variable &amp; Operators</t>
+          <t>Finish the concept check (MP), then solve the assigned variable &amp; operator problems.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -574,22 +636,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Week 1 Assignment</t>
+          <t>HW Week 1 - Variables &amp; Operators (Mock)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Complete MP questions then solve programming tasks.</t>
+          <t>Warm-up homework covering variable assignment (VA) and arithmetic operators (OP). Complete the misconception check to unlock the coding problems.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-01T23:59:00</t>
+          <t>2027-06-28T23:59:00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-07-20T00:00:00</t>
+          <t>2026-06-22T00:00:00</t>
         </is>
       </c>
     </row>
@@ -604,85 +666,115 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
+    <col width="27" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>misconception_tag</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>text_en</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>text_id</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>options_en</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>options_id</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>answer_index</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>explanation_en</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>explanation_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>option_a_misconceptions</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>option_b_misconceptions</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>option_c_misconceptions</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VA-01</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>What happens when x &lt;- 5 is executed?</t>
+          <t>After x &lt;- 5 and then x &lt;- x + 3, what is the value of x?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Apa yang terjadi saat x &lt;- 5 dijalankan?</t>
+          <t>Setelah x &lt;- 5 lalu x &lt;- x + 3, berapa nilai x?</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>x &lt;- 5</t>
+          <t>x &lt;- 5
+x &lt;- x + 3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>["Assigns 5 to x", "Compares x and 5", "Syntax error"]</t>
+          <t>["8", "3", "5"]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>["Mengisi 5 ke x", "Membandingkan x dan 5", "Error sintaks"]</t>
+          <t>["8", "3", "5"]</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -690,52 +782,74 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Explanation: &lt;- is assignment in DAP pseudocode.</t>
+          <t>x &lt;- x + 3 reads the current value of x (5) and stores 5 + 3 = 8 back into x.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Penjelasan: &lt;- adalah pengisian nilai (assignment) di pseudocode DAP.</t>
+          <t>x &lt;- x + 3 membaca nilai x saat ini (5) dan menyimpan 5 + 3 = 8 kembali ke x.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>VA-01</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>VA-02</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>What is the value of 5 + 3 * 2 in DAP?</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Berapa nilai dari 5 + 3 * 2 dalam DAP?</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>["11", "16", "13"]</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>["11", "16", "13"]</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Multiplication binds tighter than addition: 3 * 2 = 6 is computed first, then 5 + 6 = 11.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Perkalian lebih kuat daripada penjumlahan: 3 * 2 = 6 dihitung dahulu, lalu 5 + 6 = 11.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>OP-01</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>What is the output of 5 + 3 * 2?</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Berapa hasil dari 5 + 3 * 2?</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>["16", "11", "10"]</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>["16", "11", "10"]</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Explanation: Multiplication has higher precedence.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Penjelasan: Perkalian memiliki prioritas lebih tinggi.</t>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>OP</t>
         </is>
       </c>
     </row>
@@ -750,16 +864,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>problem_key</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>misconception_tag</t>
         </is>
@@ -768,24 +886,48 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>prob-assign-var-1</t>
+          <t>simple-accumulator</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VA-01</t>
+          <t>VA</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>prob-assign-var-1</t>
+          <t>variable-assign</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OP-01</t>
+          <t>VA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>remainder-calc</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>arithmetic-mix</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>OP</t>
         </is>
       </c>
     </row>
